--- a/diseases/d123/1995-1999.xlsx
+++ b/diseases/d123/1995-1999.xlsx
@@ -1413,7 +1413,7 @@
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN5" t="b">
@@ -2213,7 +2213,7 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN9" t="b">
@@ -3013,7 +3013,7 @@
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN13" t="b">
@@ -3813,7 +3813,7 @@
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN17" t="b">
@@ -4613,7 +4613,7 @@
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN21" t="b">
@@ -5413,7 +5413,7 @@
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN25" t="b">
@@ -6213,7 +6213,7 @@
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN29" t="b">
@@ -7013,7 +7013,7 @@
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN33" t="b">
@@ -7813,7 +7813,7 @@
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN37" t="b">
@@ -8613,7 +8613,7 @@
       </c>
       <c r="AM41" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN41" t="b">
@@ -9413,7 +9413,7 @@
       </c>
       <c r="AM45" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN45" t="b">
@@ -10213,7 +10213,7 @@
       </c>
       <c r="AM49" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN49" t="b">
@@ -11013,7 +11013,7 @@
       </c>
       <c r="AM53" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN53" t="b">
@@ -11813,7 +11813,7 @@
       </c>
       <c r="AM57" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN57" t="b">
@@ -12613,7 +12613,7 @@
       </c>
       <c r="AM61" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN61" t="b">
@@ -13413,7 +13413,7 @@
       </c>
       <c r="AM65" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN65" t="b">
@@ -14213,7 +14213,7 @@
       </c>
       <c r="AM69" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN69" t="b">
@@ -15013,7 +15013,7 @@
       </c>
       <c r="AM73" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN73" t="b">
@@ -15813,7 +15813,7 @@
       </c>
       <c r="AM77" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN77" t="b">
@@ -16613,7 +16613,7 @@
       </c>
       <c r="AM81" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN81" t="b">
@@ -17413,7 +17413,7 @@
       </c>
       <c r="AM85" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN85" t="b">
@@ -18213,7 +18213,7 @@
       </c>
       <c r="AM89" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN89" t="b">
@@ -19013,7 +19013,7 @@
       </c>
       <c r="AM93" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN93" t="b">
@@ -19813,7 +19813,7 @@
       </c>
       <c r="AM97" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN97" t="b">
@@ -25413,7 +25413,7 @@
       </c>
       <c r="AM125" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN125" t="b">
@@ -26213,7 +26213,7 @@
       </c>
       <c r="AM129" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN129" t="b">
@@ -27013,7 +27013,7 @@
       </c>
       <c r="AM133" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN133" t="b">
@@ -27813,7 +27813,7 @@
       </c>
       <c r="AM137" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN137" t="b">
@@ -28613,7 +28613,7 @@
       </c>
       <c r="AM141" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN141" t="b">
@@ -29413,7 +29413,7 @@
       </c>
       <c r="AM145" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN145" t="b">
@@ -30213,7 +30213,7 @@
       </c>
       <c r="AM149" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN149" t="b">
@@ -31013,7 +31013,7 @@
       </c>
       <c r="AM153" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN153" t="b">
@@ -31813,7 +31813,7 @@
       </c>
       <c r="AM157" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN157" t="b">
@@ -32613,7 +32613,7 @@
       </c>
       <c r="AM161" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN161" t="b">
@@ -33413,7 +33413,7 @@
       </c>
       <c r="AM165" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN165" t="b">
@@ -34213,7 +34213,7 @@
       </c>
       <c r="AM169" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN169" t="b">
@@ -35013,7 +35013,7 @@
       </c>
       <c r="AM173" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN173" t="b">
@@ -35813,7 +35813,7 @@
       </c>
       <c r="AM177" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN177" t="b">
@@ -36613,7 +36613,7 @@
       </c>
       <c r="AM181" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN181" t="b">
@@ -37413,7 +37413,7 @@
       </c>
       <c r="AM185" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN185" t="b">
@@ -38213,7 +38213,7 @@
       </c>
       <c r="AM189" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN189" t="b">
@@ -39013,7 +39013,7 @@
       </c>
       <c r="AM193" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN193" t="b">
@@ -39813,7 +39813,7 @@
       </c>
       <c r="AM197" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN197" t="b">
@@ -40613,7 +40613,7 @@
       </c>
       <c r="AM201" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN201" t="b">
@@ -41413,7 +41413,7 @@
       </c>
       <c r="AM205" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN205" t="b">
@@ -42213,7 +42213,7 @@
       </c>
       <c r="AM209" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN209" t="b">
@@ -43013,7 +43013,7 @@
       </c>
       <c r="AM213" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN213" t="b">
@@ -43813,7 +43813,7 @@
       </c>
       <c r="AM217" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN217" t="b">

--- a/diseases/d123/1995-1999.xlsx
+++ b/diseases/d123/1995-1999.xlsx
@@ -1413,7 +1413,7 @@
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN5" t="b">
@@ -2213,7 +2213,7 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN9" t="b">
@@ -3013,7 +3013,7 @@
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN13" t="b">
@@ -3813,7 +3813,7 @@
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN17" t="b">
@@ -4613,7 +4613,7 @@
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN21" t="b">
@@ -5413,7 +5413,7 @@
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN25" t="b">
@@ -6213,7 +6213,7 @@
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN29" t="b">
@@ -7013,7 +7013,7 @@
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN33" t="b">
@@ -7813,7 +7813,7 @@
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN37" t="b">
@@ -8613,7 +8613,7 @@
       </c>
       <c r="AM41" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN41" t="b">
@@ -9413,7 +9413,7 @@
       </c>
       <c r="AM45" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN45" t="b">
@@ -10213,7 +10213,7 @@
       </c>
       <c r="AM49" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN49" t="b">
@@ -11013,7 +11013,7 @@
       </c>
       <c r="AM53" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN53" t="b">
@@ -11813,7 +11813,7 @@
       </c>
       <c r="AM57" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN57" t="b">
@@ -12613,7 +12613,7 @@
       </c>
       <c r="AM61" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN61" t="b">
@@ -13413,7 +13413,7 @@
       </c>
       <c r="AM65" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN65" t="b">
@@ -14213,7 +14213,7 @@
       </c>
       <c r="AM69" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN69" t="b">
@@ -15013,7 +15013,7 @@
       </c>
       <c r="AM73" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN73" t="b">
@@ -15813,7 +15813,7 @@
       </c>
       <c r="AM77" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN77" t="b">
@@ -16613,7 +16613,7 @@
       </c>
       <c r="AM81" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN81" t="b">
@@ -17413,7 +17413,7 @@
       </c>
       <c r="AM85" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN85" t="b">
@@ -18213,7 +18213,7 @@
       </c>
       <c r="AM89" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN89" t="b">
@@ -19013,7 +19013,7 @@
       </c>
       <c r="AM93" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN93" t="b">
@@ -19813,7 +19813,7 @@
       </c>
       <c r="AM97" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN97" t="b">
@@ -25413,7 +25413,7 @@
       </c>
       <c r="AM125" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN125" t="b">
@@ -26213,7 +26213,7 @@
       </c>
       <c r="AM129" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN129" t="b">
@@ -27013,7 +27013,7 @@
       </c>
       <c r="AM133" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN133" t="b">
@@ -27813,7 +27813,7 @@
       </c>
       <c r="AM137" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN137" t="b">
@@ -28613,7 +28613,7 @@
       </c>
       <c r="AM141" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN141" t="b">
@@ -29413,7 +29413,7 @@
       </c>
       <c r="AM145" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN145" t="b">
@@ -30213,7 +30213,7 @@
       </c>
       <c r="AM149" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN149" t="b">
@@ -31013,7 +31013,7 @@
       </c>
       <c r="AM153" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN153" t="b">
@@ -31813,7 +31813,7 @@
       </c>
       <c r="AM157" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN157" t="b">
@@ -32613,7 +32613,7 @@
       </c>
       <c r="AM161" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN161" t="b">
@@ -33413,7 +33413,7 @@
       </c>
       <c r="AM165" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN165" t="b">
@@ -34213,7 +34213,7 @@
       </c>
       <c r="AM169" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN169" t="b">
@@ -35013,7 +35013,7 @@
       </c>
       <c r="AM173" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN173" t="b">
@@ -35813,7 +35813,7 @@
       </c>
       <c r="AM177" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN177" t="b">
@@ -36613,7 +36613,7 @@
       </c>
       <c r="AM181" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN181" t="b">
@@ -37413,7 +37413,7 @@
       </c>
       <c r="AM185" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN185" t="b">
@@ -38213,7 +38213,7 @@
       </c>
       <c r="AM189" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN189" t="b">
@@ -39013,7 +39013,7 @@
       </c>
       <c r="AM193" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN193" t="b">
@@ -39813,7 +39813,7 @@
       </c>
       <c r="AM197" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN197" t="b">
@@ -40613,7 +40613,7 @@
       </c>
       <c r="AM201" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN201" t="b">
@@ -41413,7 +41413,7 @@
       </c>
       <c r="AM205" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN205" t="b">
@@ -42213,7 +42213,7 @@
       </c>
       <c r="AM209" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN209" t="b">
@@ -43013,7 +43013,7 @@
       </c>
       <c r="AM213" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN213" t="b">
@@ -43813,7 +43813,7 @@
       </c>
       <c r="AM217" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN217" t="b">
